--- a/astro-site/public/dl/pack-appcc/03-plan-limpieza-desinfeccion.xlsx
+++ b/astro-site/public/dl/pack-appcc/03-plan-limpieza-desinfeccion.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Plan Maestro L+D" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan Maestro L+D" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Plan Maestro L+D'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -139,49 +141,49 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="17">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -541,15 +543,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B20"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -557,6 +560,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -564,9 +568,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -595,9 +597,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" t="inlineStr"/>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
         <is>
@@ -605,9 +605,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" t="inlineStr"/>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -650,13 +648,19 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" t="inlineStr"/>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/pack-appcc · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -664,7 +668,16 @@
   <mergeCells count="1">
     <mergeCell ref="B2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -673,18 +686,18 @@
   <sheetPr>
     <tabColor rgb="004CAF50"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="25"/>
-    <col customWidth="1" max="2" min="2" width="30"/>
-    <col customWidth="1" max="3" min="3" width="15"/>
-    <col customWidth="1" max="4" min="4" width="25"/>
-    <col customWidth="1" max="5" min="5" width="20"/>
-    <col customWidth="1" max="6" min="6" width="25"/>
-    <col customWidth="1" max="7" min="7" width="20"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -701,6 +714,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1595,6 +1609,8 @@
       <c r="F41" s="15" t="n"/>
       <c r="G41" s="15" t="n"/>
     </row>
+    <row r="42"/>
+    <row r="43"/>
     <row r="44">
       <c r="A44" s="16" t="inlineStr">
         <is>
@@ -1614,11 +1630,19 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="C6 C7 C8 C9 C10 C11 C12 C15 C16 C17 C18 C21 C22 C23 C26 C27 C30 C31 C32 C33 C34 C35 C36 C37 C38 C39 C40 C41" type="list">
+    <dataValidation sqref="C6 C7 C8 C9 C10 C11 C12 C15 C16 C17 C18 C21 C22 C23 C26 C27 C30 C31 C32 C33 C34 C35 C36 C37 C38 C39 C40 C41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Cada servicio,Diaria,Semanal,Quincenal,Mensual,Trimestral"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="landscape"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/pack-appcc/03-plan-limpieza-desinfeccion.xlsx
+++ b/astro-site/public/dl/pack-appcc/03-plan-limpieza-desinfeccion.xlsx
@@ -2593,19 +2593,19 @@
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A53:I53"/>
+    <mergeCell ref="A57:I57"/>
+    <mergeCell ref="A55:I55"/>
     <mergeCell ref="A43:I43"/>
     <mergeCell ref="A27:I27"/>
-    <mergeCell ref="A55:I55"/>
-    <mergeCell ref="A57:I57"/>
     <mergeCell ref="A51:E51"/>
     <mergeCell ref="A58:I58"/>
     <mergeCell ref="A35:I35"/>
-    <mergeCell ref="A38:I38"/>
+    <mergeCell ref="A22:I22"/>
     <mergeCell ref="A54:I54"/>
     <mergeCell ref="A31:I31"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A22:I22"/>
     <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A38:I38"/>
     <mergeCell ref="A56:I56"/>
   </mergeCells>
   <conditionalFormatting sqref="F6:F21">
@@ -3184,9 +3184,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A32:H32"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A32:H32"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F28">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
